--- a/test-harness/.tmp/OptionSets_Export_2026-04-23.xlsx
+++ b/test-harness/.tmp/OptionSets_Export_2026-04-23.xlsx
@@ -616,7 +616,7 @@
         <v>0-14 years</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -636,7 +636,7 @@
         <v>15-19 years</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -656,7 +656,7 @@
         <v>20-24 years</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -676,7 +676,7 @@
         <v>25 years and above</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
         <v>Penicillin</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>SULFA</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>Anticonvulsants</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
         <v>NSAIDS</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -776,7 +776,7 @@
         <v>Other</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -796,7 +796,7 @@
         <v>None</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -816,7 +816,7 @@
         <v>Penicillin</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -836,7 +836,7 @@
         <v>Other medicine - please specify</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -856,7 +856,7 @@
         <v>Other severe allergy - please specify</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -876,7 +876,7 @@
         <v>AL</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -896,7 +896,7 @@
         <v>AS+AQ</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -916,7 +916,7 @@
         <v>AS+MQ</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -936,7 +936,7 @@
         <v>AS+SP</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -956,7 +956,7 @@
         <v>AS-SP</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -976,7 +976,7 @@
         <v>DHA-PPQ</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -996,7 +996,7 @@
         <v>AL+PQ</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1016,7 +1016,7 @@
         <v>DHA-PPQ+PQ</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1036,7 +1036,7 @@
         <v>AS+MQ+PQ</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1056,7 +1056,7 @@
         <v>AS+SP+PQ</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1076,7 +1076,7 @@
         <v>OTHER</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1096,7 +1096,7 @@
         <v>NVP only</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1116,7 +1116,7 @@
         <v>AZT and NVP</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1136,7 +1136,7 @@
         <v>AZT and 3TC and HAART</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1156,7 +1156,7 @@
         <v>NA</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1176,7 +1176,7 @@
         <v>None</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1196,7 +1196,7 @@
         <v>Ongoing</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1216,7 +1216,7 @@
         <v>Initiated</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1236,7 +1236,7 @@
         <v>None</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1256,7 +1256,7 @@
         <v>Chronic hypertension</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1276,7 +1276,7 @@
         <v>Autoimmune disease</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1296,7 +1296,7 @@
         <v>Diabetes</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1316,7 +1316,7 @@
         <v>HIV</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1336,7 +1336,7 @@
         <v>Renal disease</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -1356,7 +1356,7 @@
         <v>Other - please specify</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -1376,7 +1376,7 @@
         <v>Single or widow</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1396,7 +1396,7 @@
         <v>Married (conjugal cohabitation)</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1416,7 +1416,7 @@
         <v>INPUT</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1436,7 +1436,7 @@
         <v>ACTIVITY</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1456,7 +1456,7 @@
         <v>OUTPUT</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1476,7 +1476,7 @@
         <v>IMPACT</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1496,7 +1496,7 @@
         <v>Active</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1516,7 +1516,7 @@
         <v>Residual non-active</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1536,7 +1536,7 @@
         <v>Cleared</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
